--- a/xls/square_12_tri3_7.xlsx
+++ b/xls/square_12_tri3_7.xlsx
@@ -418,7 +418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -482,13 +482,13 @@
         <v>294</v>
       </c>
       <c r="I7">
-        <v>2.827903973218562</v>
+        <v>2.8279038220544814</v>
       </c>
       <c r="J7">
-        <v>-0.5391346104864433</v>
+        <v>-0.5391346245132177</v>
       </c>
       <c r="K7">
-        <v>0.007438645457612111</v>
+        <v>0.007438513509001729</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -517,13 +517,13 @@
         <v>384</v>
       </c>
       <c r="I8">
-        <v>-1.6072887108830984</v>
+        <v>-1.6072887327820504</v>
       </c>
       <c r="J8">
-        <v>-1.5387119809569887</v>
+        <v>-1.5387118184491266</v>
       </c>
       <c r="K8">
-        <v>-0.9265706069303323</v>
+        <v>-0.9265706023189737</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -552,13 +552,13 @@
         <v>486</v>
       </c>
       <c r="I9">
-        <v>-1.6213488703930234</v>
+        <v>-1.6213488581930842</v>
       </c>
       <c r="J9">
-        <v>-1.4619495847190689</v>
+        <v>-1.4619496144433315</v>
       </c>
       <c r="K9">
-        <v>-0.7124078240367121</v>
+        <v>-0.7124079076706075</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -587,13 +587,13 @@
         <v>600</v>
       </c>
       <c r="I10">
-        <v>-1.500468687591801</v>
+        <v>-1.500468276402105</v>
       </c>
       <c r="J10">
-        <v>-1.1837807515689511</v>
+        <v>-1.1837806234737687</v>
       </c>
       <c r="K10">
-        <v>-0.3630093208585441</v>
+        <v>-0.363009357132323</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -622,13 +622,13 @@
         <v>726</v>
       </c>
       <c r="I11">
-        <v>-0.9601155008095257</v>
+        <v>-0.9601155325737992</v>
       </c>
       <c r="J11">
-        <v>-0.7069738199777906</v>
+        <v>-0.7069738323612019</v>
       </c>
       <c r="K11">
-        <v>0.13039334567484612</v>
+        <v>0.1303933465066091</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -657,13 +657,13 @@
         <v>864</v>
       </c>
       <c r="I12">
-        <v>-1.4800173255381956</v>
+        <v>-1.480017327692089</v>
       </c>
       <c r="J12">
-        <v>-1.2480306153824743</v>
+        <v>-1.2480307047212544</v>
       </c>
       <c r="K12">
-        <v>-0.400910721242305</v>
+        <v>-0.40091067097328364</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -692,13 +692,13 @@
         <v>1014</v>
       </c>
       <c r="I13">
-        <v>-0.0011507815345085863</v>
+        <v>-0.0011507760505548642</v>
       </c>
       <c r="J13">
-        <v>-0.005343411286446288</v>
+        <v>-0.005343409395923258</v>
       </c>
       <c r="K13">
-        <v>2.021791751338464</v>
+        <v>2.021791726397749</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -727,13 +727,13 @@
         <v>1176</v>
       </c>
       <c r="I14">
-        <v>-5.534972385631834e-5</v>
+        <v>-5.534972385246054e-5</v>
       </c>
       <c r="J14">
-        <v>-4.207810336397423e-5</v>
+        <v>-4.207810336349202e-5</v>
       </c>
       <c r="K14">
-        <v>2.1203245320432447</v>
+        <v>2.1203245320510313</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -762,13 +762,13 @@
         <v>1350</v>
       </c>
       <c r="I15">
-        <v>-2.4295092465972887e-5</v>
+        <v>-2.4295092466840832e-5</v>
       </c>
       <c r="J15">
-        <v>-1.6648264808286546e-5</v>
+        <v>-1.6648264809058037e-5</v>
       </c>
       <c r="K15">
-        <v>1.914258651976214</v>
+        <v>1.9142586515660158</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -797,13 +797,573 @@
         <v>1536</v>
       </c>
       <c r="I16">
-        <v>1.4603291592170226e-6</v>
+        <v>1.4603291590241576e-6</v>
       </c>
       <c r="J16">
-        <v>3.1555696580839724e-7</v>
+        <v>3.1555696571196455e-7</v>
       </c>
       <c r="K16">
-        <v>1.4174257712624712</v>
+        <v>1.4174257710870273</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17">
+        <v>64</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17">
+        <v>169</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17">
+        <v>324</v>
+      </c>
+      <c r="G17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17">
+        <v>1734</v>
+      </c>
+      <c r="I17">
+        <v>2.0506496535587655e-6</v>
+      </c>
+      <c r="J17">
+        <v>6.204586392069419e-7</v>
+      </c>
+      <c r="K17">
+        <v>1.419054274898621</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18">
+        <v>64</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18">
+        <v>169</v>
+      </c>
+      <c r="E18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18">
+        <v>361</v>
+      </c>
+      <c r="G18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18">
+        <v>1944</v>
+      </c>
+      <c r="I18">
+        <v>1.161767949146358e-6</v>
+      </c>
+      <c r="J18">
+        <v>4.005528110179645e-7</v>
+      </c>
+      <c r="K18">
+        <v>1.2524678669159852</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19">
+        <v>64</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19">
+        <v>169</v>
+      </c>
+      <c r="E19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19">
+        <v>400</v>
+      </c>
+      <c r="G19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19">
+        <v>2166</v>
+      </c>
+      <c r="I19">
+        <v>1.1150534981506836e-7</v>
+      </c>
+      <c r="J19">
+        <v>-2.6234971953428256e-8</v>
+      </c>
+      <c r="K19">
+        <v>1.082091058161052</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20">
+        <v>64</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20">
+        <v>169</v>
+      </c>
+      <c r="E20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20">
+        <v>441</v>
+      </c>
+      <c r="G20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20">
+        <v>2400</v>
+      </c>
+      <c r="I20">
+        <v>1.5308412145771594e-8</v>
+      </c>
+      <c r="J20">
+        <v>-4.158555242542678e-8</v>
+      </c>
+      <c r="K20">
+        <v>0.9705442934380756</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21">
+        <v>64</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21">
+        <v>169</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21">
+        <v>484</v>
+      </c>
+      <c r="G21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21">
+        <v>2646</v>
+      </c>
+      <c r="I21">
+        <v>-6.722794299007832e-8</v>
+      </c>
+      <c r="J21">
+        <v>-7.293069930334505e-8</v>
+      </c>
+      <c r="K21">
+        <v>0.9158344530960957</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22">
+        <v>64</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22">
+        <v>169</v>
+      </c>
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22">
+        <v>529</v>
+      </c>
+      <c r="G22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22">
+        <v>2904</v>
+      </c>
+      <c r="I22">
+        <v>-6.392140767853268e-8</v>
+      </c>
+      <c r="J22">
+        <v>-6.334149847108679e-8</v>
+      </c>
+      <c r="K22">
+        <v>0.8655621440583122</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23">
+        <v>64</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23">
+        <v>169</v>
+      </c>
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23">
+        <v>576</v>
+      </c>
+      <c r="G23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23">
+        <v>3174</v>
+      </c>
+      <c r="I23">
+        <v>-5.599606847493617e-8</v>
+      </c>
+      <c r="J23">
+        <v>-5.723912777351076e-8</v>
+      </c>
+      <c r="K23">
+        <v>0.8474294634975029</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24">
+        <v>64</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24">
+        <v>169</v>
+      </c>
+      <c r="E24" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24">
+        <v>625</v>
+      </c>
+      <c r="G24" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24">
+        <v>3456</v>
+      </c>
+      <c r="I24">
+        <v>-8.065459568882729e-8</v>
+      </c>
+      <c r="J24">
+        <v>-6.881425319384972e-8</v>
+      </c>
+      <c r="K24">
+        <v>0.8402320634672303</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25">
+        <v>64</v>
+      </c>
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25">
+        <v>169</v>
+      </c>
+      <c r="E25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25">
+        <v>676</v>
+      </c>
+      <c r="G25" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25">
+        <v>3750</v>
+      </c>
+      <c r="I25">
+        <v>-8.101095694337288e-8</v>
+      </c>
+      <c r="J25">
+        <v>-6.864961016428236e-8</v>
+      </c>
+      <c r="K25">
+        <v>0.8380821211305242</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26">
+        <v>64</v>
+      </c>
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26">
+        <v>169</v>
+      </c>
+      <c r="E26" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26">
+        <v>729</v>
+      </c>
+      <c r="G26" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26">
+        <v>4056</v>
+      </c>
+      <c r="I26">
+        <v>-5.621305737110008e-8</v>
+      </c>
+      <c r="J26">
+        <v>-5.63904599929157e-8</v>
+      </c>
+      <c r="K26">
+        <v>0.8403220155535209</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27">
+        <v>64</v>
+      </c>
+      <c r="C27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27">
+        <v>169</v>
+      </c>
+      <c r="E27" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27">
+        <v>784</v>
+      </c>
+      <c r="G27" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27">
+        <v>4374</v>
+      </c>
+      <c r="I27">
+        <v>-6.027454136491855e-8</v>
+      </c>
+      <c r="J27">
+        <v>-5.849156115955895e-8</v>
+      </c>
+      <c r="K27">
+        <v>0.8418227829159816</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28">
+        <v>64</v>
+      </c>
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28">
+        <v>169</v>
+      </c>
+      <c r="E28" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28">
+        <v>841</v>
+      </c>
+      <c r="G28" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28">
+        <v>4704</v>
+      </c>
+      <c r="I28">
+        <v>-7.300502244449836e-8</v>
+      </c>
+      <c r="J28">
+        <v>-6.573487869166505e-8</v>
+      </c>
+      <c r="K28">
+        <v>0.8475755591525466</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29">
+        <v>64</v>
+      </c>
+      <c r="C29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29">
+        <v>169</v>
+      </c>
+      <c r="E29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29">
+        <v>900</v>
+      </c>
+      <c r="G29" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29">
+        <v>5046</v>
+      </c>
+      <c r="I29">
+        <v>-5.6488270294068084e-8</v>
+      </c>
+      <c r="J29">
+        <v>-5.610841688233073e-8</v>
+      </c>
+      <c r="K29">
+        <v>0.8379143245713191</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30">
+        <v>64</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30">
+        <v>169</v>
+      </c>
+      <c r="E30" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30">
+        <v>961</v>
+      </c>
+      <c r="G30" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30">
+        <v>5400</v>
+      </c>
+      <c r="I30">
+        <v>-5.639951970599129e-8</v>
+      </c>
+      <c r="J30">
+        <v>-5.581755576757585e-8</v>
+      </c>
+      <c r="K30">
+        <v>0.8352039768957421</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31">
+        <v>64</v>
+      </c>
+      <c r="C31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31">
+        <v>169</v>
+      </c>
+      <c r="E31" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31">
+        <v>1024</v>
+      </c>
+      <c r="G31" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31">
+        <v>5766</v>
+      </c>
+      <c r="I31">
+        <v>-6.789734117877849e-8</v>
+      </c>
+      <c r="J31">
+        <v>-6.13872049240738e-8</v>
+      </c>
+      <c r="K31">
+        <v>0.8331323371873202</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32">
+        <v>64</v>
+      </c>
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32">
+        <v>169</v>
+      </c>
+      <c r="E32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32">
+        <v>1089</v>
+      </c>
+      <c r="G32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32">
+        <v>6144</v>
+      </c>
+      <c r="I32">
+        <v>-6.301037040578647e-8</v>
+      </c>
+      <c r="J32">
+        <v>-5.856573608108961e-8</v>
+      </c>
+      <c r="K32">
+        <v>0.8301840767802686</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_12_tri3_7.xlsx
+++ b/xls/square_12_tri3_7.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>64</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5">
+        <v>169</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5">
+        <v>36</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5">
+        <v>150</v>
+      </c>
+      <c r="I5">
+        <v>26.068362949983417</v>
+      </c>
+      <c r="J5">
+        <v>12.042855055130312</v>
+      </c>
+      <c r="K5">
+        <v>10.163531103956597</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6">
+        <v>64</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>169</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6">
+        <v>49</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6">
+        <v>216</v>
+      </c>
+      <c r="I6">
+        <v>14.734703018685739</v>
+      </c>
+      <c r="J6">
+        <v>2.5812694302996557</v>
+      </c>
+      <c r="K6">
+        <v>2.900148303648</v>
+      </c>
+    </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
         <v>11</v>
